--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.00845820783045732</v>
       </c>
       <c r="C2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>43814865</v>
+        <v>4063831</v>
       </c>
       <c r="L2" t="n">
-        <v>23595936</v>
+        <v>1709147</v>
       </c>
       <c r="M2" t="n">
-        <v>5541493</v>
+        <v>315103</v>
       </c>
       <c r="N2" t="n">
-        <v>247140</v>
+        <v>7032</v>
       </c>
       <c r="O2" t="n">
-        <v>3251367</v>
+        <v>177380</v>
       </c>
       <c r="P2" t="n">
-        <v>1262656</v>
+        <v>61746</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999988317489624</v>
+        <v>0.9999572038650513</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8463183045387268</v>
+        <v>0.7280555963516235</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7199983596801758</v>
+        <v>0.5527631640434265</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6538532376289368</v>
+        <v>0.4244697690010071</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2502404749393463</v>
+        <v>0.05600152909755707</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7056716084480286</v>
+        <v>0.4716098308563232</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8136136531829834</v>
+        <v>0.6264940500259399</v>
       </c>
       <c r="X2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63129780</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559409618377686</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116660952568054</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582287430763245</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617533564567566</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.902009129524231</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027664927559576</v>
       </c>
       <c r="C3" t="n">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>43814865</v>
+        <v>4063831</v>
       </c>
       <c r="E3" t="n">
-        <v>6074292</v>
+        <v>857939</v>
       </c>
       <c r="F3" t="n">
-        <v>161817</v>
+        <v>32673</v>
       </c>
       <c r="G3" t="n">
-        <v>14176</v>
+        <v>2835</v>
       </c>
       <c r="H3" t="n">
-        <v>9697</v>
+        <v>2509</v>
       </c>
       <c r="I3" t="n">
-        <v>766</v>
+        <v>283</v>
       </c>
       <c r="J3" t="n">
-        <v>100165483</v>
+        <v>10016352</v>
       </c>
       <c r="K3" t="n">
-        <v>105263982</v>
+        <v>9851560</v>
       </c>
       <c r="L3" t="n">
-        <v>121310409</v>
+        <v>11627609</v>
       </c>
       <c r="M3" t="n">
-        <v>151009807</v>
+        <v>14960502</v>
       </c>
       <c r="N3" t="n">
-        <v>161661966</v>
+        <v>16121256</v>
       </c>
       <c r="O3" t="n">
-        <v>156839458</v>
+        <v>15618955</v>
       </c>
       <c r="P3" t="n">
-        <v>161072132</v>
+        <v>16098983</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.874971866607666</v>
+        <v>0.8193022608757019</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7191839218139648</v>
+        <v>0.5149379372596741</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5925112366676331</v>
+        <v>0.3345553874969482</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2765778303146362</v>
+        <v>0.07830037176609039</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6374691724777222</v>
+        <v>0.3465068936347961</v>
       </c>
       <c r="W3" t="n">
-        <v>0.652665913105011</v>
+        <v>0.318598598241806</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47949558</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1972670</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84826</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>68106</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>280</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100166220</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>111010280</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127594505</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152619092</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>162100491</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157696105</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>161228809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575406908988953</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097784161567688</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85721355676651</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.661096453666687</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014128446578979</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03198836053224347</v>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>7367803</v>
+        <v>1366430</v>
       </c>
       <c r="E4" t="n">
-        <v>23595936</v>
+        <v>1709147</v>
       </c>
       <c r="F4" t="n">
-        <v>1574369</v>
+        <v>192980</v>
       </c>
       <c r="G4" t="n">
-        <v>96089</v>
+        <v>18080</v>
       </c>
       <c r="H4" t="n">
-        <v>159869</v>
+        <v>29071</v>
       </c>
       <c r="I4" t="n">
-        <v>15157</v>
+        <v>3378</v>
       </c>
       <c r="J4" t="n">
-        <v>737</v>
+        <v>270</v>
       </c>
       <c r="K4" t="n">
-        <v>7956278</v>
+        <v>1517928</v>
       </c>
       <c r="L4" t="n">
-        <v>9176271</v>
+        <v>1382859</v>
       </c>
       <c r="M4" t="n">
-        <v>2933640</v>
+        <v>427242</v>
       </c>
       <c r="N4" t="n">
-        <v>740470</v>
+        <v>118536</v>
       </c>
       <c r="O4" t="n">
-        <v>1356112</v>
+        <v>198736</v>
       </c>
       <c r="P4" t="n">
-        <v>289255</v>
+        <v>36812</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999994158744812</v>
+        <v>0.9999786019325256</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8604065775871277</v>
+        <v>0.7709885835647583</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7195909023284912</v>
+        <v>0.5331805348396301</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6216726899147034</v>
+        <v>0.3741869330406189</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2627508342266083</v>
+        <v>0.06529975682497025</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6698387265205383</v>
+        <v>0.3994932472705841</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7243065237998962</v>
+        <v>0.422392725944519</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2063963</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29849211</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>828823</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55262</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11381</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2209980</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2892175</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1324355</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301945</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499465</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567400813102722</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107212424278259</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577207922935486</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614247560501099</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017109274864197</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>415553</v>
+        <v>112218</v>
       </c>
       <c r="E5" t="n">
-        <v>2517175</v>
+        <v>399680</v>
       </c>
       <c r="F5" t="n">
-        <v>5541493</v>
+        <v>315103</v>
       </c>
       <c r="G5" t="n">
-        <v>235458</v>
+        <v>32944</v>
       </c>
       <c r="H5" t="n">
-        <v>583427</v>
+        <v>71686</v>
       </c>
       <c r="I5" t="n">
-        <v>59367</v>
+        <v>10180</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6260875</v>
+        <v>896281</v>
       </c>
       <c r="L5" t="n">
-        <v>9213384</v>
+        <v>1609985</v>
       </c>
       <c r="M5" t="n">
-        <v>3811060</v>
+        <v>626753</v>
       </c>
       <c r="N5" t="n">
-        <v>646424</v>
+        <v>82776</v>
       </c>
       <c r="O5" t="n">
-        <v>1849063</v>
+        <v>334529</v>
       </c>
       <c r="P5" t="n">
-        <v>671957</v>
+        <v>132059</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999954700469971</v>
+        <v>0.9999834895133972</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9129363298416138</v>
+        <v>0.8521574735641479</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8873845338821411</v>
+        <v>0.8167227506637573</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9586964845657349</v>
+        <v>0.9354549646377563</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9915068745613098</v>
+        <v>0.987671971321106</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9803720116615295</v>
+        <v>0.9673436284065247</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941136837005615</v>
+        <v>0.9896585941314697</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80454</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>857060</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8017135</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99758</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291816</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2126182</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2960109</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1335418</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302832</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502837</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734460115432739</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641615152359009</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837119579315186</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962964653968811</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938620328903198</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983729124069214</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>136107</v>
+        <v>23341</v>
       </c>
       <c r="E6" t="n">
-        <v>211674</v>
+        <v>25574</v>
       </c>
       <c r="F6" t="n">
-        <v>206849</v>
+        <v>24697</v>
       </c>
       <c r="G6" t="n">
-        <v>247140</v>
+        <v>7032</v>
       </c>
       <c r="H6" t="n">
-        <v>83038</v>
+        <v>8069</v>
       </c>
       <c r="I6" t="n">
-        <v>8641</v>
+        <v>1065</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65084</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53535</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109471</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590732</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69932</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>34792</v>
+        <v>14811</v>
       </c>
       <c r="E7" t="n">
-        <v>341928</v>
+        <v>89664</v>
       </c>
       <c r="F7" t="n">
-        <v>915268</v>
+        <v>154698</v>
       </c>
       <c r="G7" t="n">
-        <v>351690</v>
+        <v>53418</v>
       </c>
       <c r="H7" t="n">
-        <v>3251367</v>
+        <v>177380</v>
       </c>
       <c r="I7" t="n">
-        <v>205324</v>
+        <v>21906</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8100</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297921</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76159</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597593</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>75</v>
       </c>
       <c r="D8" t="n">
-        <v>2023</v>
+        <v>1128</v>
       </c>
       <c r="E8" t="n">
-        <v>31202</v>
+        <v>10002</v>
       </c>
       <c r="F8" t="n">
-        <v>75337</v>
+        <v>22194</v>
       </c>
       <c r="G8" t="n">
-        <v>43057</v>
+        <v>11259</v>
       </c>
       <c r="H8" t="n">
-        <v>520081</v>
+        <v>87401</v>
       </c>
       <c r="I8" t="n">
-        <v>1262656</v>
+        <v>61746</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
